--- a/данные/НашаШкола_5-11_нагрузка.xlsx
+++ b/данные/НашаШкола_5-11_нагрузка.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Load" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I397"/>
+  <dimension ref="A1:K409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,16 @@
           <t>UnavailSlots</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Pair</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,6 +501,8 @@
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,6 +528,8 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -545,6 +559,8 @@
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -574,6 +590,8 @@
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -611,6 +629,8 @@
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -640,6 +660,8 @@
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -669,6 +691,8 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -698,6 +722,8 @@
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -727,6 +753,8 @@
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -756,6 +784,8 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -785,6 +815,8 @@
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -814,6 +846,8 @@
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -851,6 +885,8 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -880,6 +916,8 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -909,6 +947,8 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -946,6 +986,8 @@
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -975,6 +1017,8 @@
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1000,6 +1044,8 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1029,6 +1075,8 @@
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1058,6 +1106,8 @@
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1087,6 +1137,8 @@
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1116,6 +1168,8 @@
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1145,6 +1199,8 @@
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1174,6 +1230,8 @@
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1203,6 +1261,8 @@
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1240,6 +1300,8 @@
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1269,6 +1331,8 @@
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1298,6 +1362,8 @@
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1323,6 +1389,8 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1360,6 +1428,8 @@
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1389,6 +1459,8 @@
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1418,6 +1490,8 @@
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1447,6 +1521,8 @@
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1476,6 +1552,8 @@
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1513,6 +1591,8 @@
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1542,6 +1622,8 @@
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1571,6 +1653,8 @@
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1600,6 +1684,8 @@
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1629,6 +1715,8 @@
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1658,6 +1746,8 @@
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1687,6 +1777,8 @@
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1716,6 +1808,8 @@
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1741,6 +1835,8 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1778,6 +1874,8 @@
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1807,6 +1905,8 @@
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1836,6 +1936,8 @@
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1865,6 +1967,8 @@
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1894,6 +1998,8 @@
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1931,6 +2037,8 @@
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1960,6 +2068,8 @@
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1989,6 +2099,8 @@
       </c>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2018,6 +2130,8 @@
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2047,6 +2161,10 @@
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2076,6 +2194,10 @@
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2105,6 +2227,10 @@
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2134,6 +2260,10 @@
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2163,6 +2293,10 @@
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2188,6 +2322,10 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2225,6 +2363,10 @@
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2254,6 +2396,10 @@
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2283,6 +2429,10 @@
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2320,6 +2470,10 @@
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2349,6 +2503,10 @@
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2378,6 +2536,10 @@
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2407,6 +2569,10 @@
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2444,6 +2610,10 @@
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2473,6 +2643,10 @@
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2502,6 +2676,10 @@
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2539,6 +2717,10 @@
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2568,6 +2750,10 @@
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2597,6 +2783,10 @@
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2626,6 +2816,10 @@
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2655,6 +2849,10 @@
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2680,6 +2878,10 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2709,6 +2911,10 @@
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2738,6 +2944,10 @@
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2767,6 +2977,10 @@
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2804,6 +3018,10 @@
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2833,6 +3051,10 @@
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2870,6 +3092,10 @@
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2899,6 +3125,10 @@
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2928,6 +3158,10 @@
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2965,6 +3199,10 @@
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2990,6 +3228,10 @@
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3019,6 +3261,10 @@
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3048,6 +3294,10 @@
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3077,6 +3327,10 @@
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3106,6 +3360,10 @@
       </c>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3135,6 +3393,10 @@
       </c>
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3164,6 +3426,10 @@
       </c>
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3193,6 +3459,10 @@
       </c>
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3222,6 +3492,10 @@
       </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3251,6 +3525,10 @@
       </c>
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3280,6 +3558,10 @@
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3317,6 +3599,10 @@
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3354,6 +3640,10 @@
       </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3383,6 +3673,10 @@
       </c>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3412,6 +3706,10 @@
       </c>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3441,6 +3739,10 @@
       </c>
       <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3470,6 +3772,10 @@
       </c>
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3499,6 +3805,10 @@
       </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3528,6 +3838,10 @@
       </c>
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3557,6 +3871,10 @@
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3586,6 +3904,10 @@
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3623,6 +3945,10 @@
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3648,6 +3974,10 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3685,6 +4015,10 @@
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3714,6 +4048,10 @@
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3743,6 +4081,10 @@
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3772,6 +4114,10 @@
       </c>
       <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3809,6 +4155,10 @@
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3838,6 +4188,10 @@
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3867,6 +4221,10 @@
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3896,6 +4254,10 @@
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3925,6 +4287,10 @@
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3954,6 +4320,10 @@
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3991,6 +4361,10 @@
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4016,6 +4390,10 @@
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4053,6 +4431,10 @@
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4082,6 +4464,10 @@
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4111,6 +4497,10 @@
       </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4140,6 +4530,10 @@
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4177,6 +4571,10 @@
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4206,6 +4604,10 @@
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4235,6 +4637,10 @@
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4264,6 +4670,10 @@
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4293,6 +4703,10 @@
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4322,6 +4736,10 @@
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4351,6 +4769,10 @@
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4380,6 +4802,10 @@
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4417,6 +4843,10 @@
       </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4446,6 +4876,10 @@
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4475,6 +4909,10 @@
       </c>
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4504,6 +4942,10 @@
       </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4533,6 +4975,10 @@
       </c>
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4570,6 +5016,10 @@
       </c>
       <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4599,6 +5049,10 @@
       </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4628,6 +5082,10 @@
       </c>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4657,6 +5115,10 @@
       </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4686,6 +5148,10 @@
       </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4715,6 +5181,10 @@
       </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4744,6 +5214,10 @@
       </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4781,6 +5255,10 @@
       </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4806,6 +5284,10 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4835,6 +5317,10 @@
       </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4864,6 +5350,10 @@
       </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4893,6 +5383,10 @@
       </c>
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4922,6 +5416,10 @@
       </c>
       <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4951,6 +5449,10 @@
       </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4988,6 +5490,10 @@
       </c>
       <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5025,6 +5531,10 @@
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5054,6 +5564,10 @@
       </c>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5091,6 +5605,10 @@
       </c>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5116,6 +5634,10 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5145,6 +5667,10 @@
       </c>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5174,6 +5700,10 @@
       </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5203,6 +5733,10 @@
       </c>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5232,6 +5766,10 @@
       </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5261,6 +5799,10 @@
       </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5290,6 +5832,10 @@
       </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5319,6 +5865,10 @@
       </c>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5348,6 +5898,10 @@
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5377,6 +5931,10 @@
       </c>
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5406,6 +5964,10 @@
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5435,6 +5997,10 @@
       </c>
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5460,6 +6026,10 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5489,6 +6059,10 @@
       </c>
       <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5526,6 +6100,10 @@
       </c>
       <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5563,6 +6141,10 @@
       </c>
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5592,6 +6174,10 @@
       </c>
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5617,6 +6203,10 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5646,6 +6236,10 @@
       </c>
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5675,6 +6269,10 @@
       </c>
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5704,6 +6302,10 @@
       </c>
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5729,6 +6331,10 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5758,6 +6364,10 @@
       </c>
       <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5787,6 +6397,10 @@
       </c>
       <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5816,6 +6430,10 @@
       </c>
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5845,6 +6463,10 @@
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5870,6 +6492,10 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5899,6 +6525,8 @@
       </c>
       <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5928,6 +6556,8 @@
       </c>
       <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5953,6 +6583,8 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5990,6 +6622,8 @@
       </c>
       <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6027,6 +6661,8 @@
       </c>
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6056,6 +6692,8 @@
       </c>
       <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6085,6 +6723,8 @@
       </c>
       <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6114,6 +6754,8 @@
       </c>
       <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6143,6 +6785,8 @@
       </c>
       <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6172,6 +6816,8 @@
       </c>
       <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6201,6 +6847,8 @@
       </c>
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6230,6 +6878,8 @@
       </c>
       <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6259,6 +6909,8 @@
       </c>
       <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6296,6 +6948,8 @@
       </c>
       <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6325,6 +6979,8 @@
       </c>
       <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6354,6 +7010,8 @@
       </c>
       <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6383,6 +7041,8 @@
       </c>
       <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6412,6 +7072,8 @@
       </c>
       <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6441,6 +7103,8 @@
       </c>
       <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6466,6 +7130,8 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6495,6 +7161,8 @@
       </c>
       <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6524,6 +7192,8 @@
       </c>
       <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6553,6 +7223,8 @@
       </c>
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6590,6 +7262,8 @@
       </c>
       <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -6619,6 +7293,8 @@
       </c>
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -6648,6 +7324,8 @@
       </c>
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6685,6 +7363,8 @@
       </c>
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6714,6 +7394,8 @@
       </c>
       <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6751,6 +7433,8 @@
       </c>
       <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6780,6 +7464,8 @@
       </c>
       <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6809,6 +7495,8 @@
       </c>
       <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6838,6 +7526,8 @@
       </c>
       <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6867,6 +7557,8 @@
       </c>
       <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6896,6 +7588,8 @@
       </c>
       <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6933,6 +7627,8 @@
       </c>
       <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -6962,6 +7658,8 @@
       </c>
       <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -6991,6 +7689,8 @@
       </c>
       <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7020,6 +7720,8 @@
       </c>
       <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7057,6 +7759,8 @@
       </c>
       <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7082,6 +7786,8 @@
       <c r="G221" t="inlineStr"/>
       <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7111,6 +7817,8 @@
       </c>
       <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7148,6 +7856,8 @@
       </c>
       <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7177,6 +7887,8 @@
       </c>
       <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7206,6 +7918,8 @@
       </c>
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7235,6 +7949,8 @@
       </c>
       <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7264,6 +7980,8 @@
       </c>
       <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7293,6 +8011,8 @@
       </c>
       <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7322,6 +8042,8 @@
       </c>
       <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7351,6 +8073,8 @@
       </c>
       <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7380,6 +8104,8 @@
       </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7409,6 +8135,8 @@
       </c>
       <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7438,6 +8166,8 @@
       </c>
       <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7463,6 +8193,8 @@
       <c r="G234" t="inlineStr"/>
       <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7492,6 +8224,8 @@
       </c>
       <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7521,6 +8255,8 @@
       </c>
       <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -7550,6 +8286,8 @@
       </c>
       <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -7587,6 +8325,8 @@
       </c>
       <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -7616,6 +8356,8 @@
       </c>
       <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -7645,6 +8387,8 @@
       </c>
       <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -7682,6 +8426,8 @@
       </c>
       <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -7711,6 +8457,8 @@
       </c>
       <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -7740,6 +8488,8 @@
       </c>
       <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -7769,6 +8519,8 @@
       </c>
       <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7798,6 +8550,8 @@
       </c>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7835,6 +8589,8 @@
       </c>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7864,6 +8620,8 @@
       </c>
       <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7893,6 +8651,8 @@
       </c>
       <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7922,6 +8682,8 @@
       </c>
       <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7947,6 +8709,8 @@
       <c r="G250" t="inlineStr"/>
       <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7976,6 +8740,8 @@
       </c>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8013,6 +8779,8 @@
       </c>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8050,6 +8818,8 @@
       </c>
       <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8079,6 +8849,8 @@
       </c>
       <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8108,6 +8880,8 @@
       </c>
       <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8137,6 +8911,8 @@
       </c>
       <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8166,6 +8942,8 @@
       </c>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8195,6 +8973,8 @@
       </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8232,6 +9012,8 @@
       </c>
       <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8261,6 +9043,8 @@
       </c>
       <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8290,6 +9074,8 @@
       </c>
       <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8319,6 +9105,8 @@
       </c>
       <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8348,6 +9136,8 @@
       </c>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8377,6 +9167,8 @@
       </c>
       <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8406,6 +9198,8 @@
       </c>
       <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8435,6 +9229,8 @@
       </c>
       <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8464,6 +9260,8 @@
       </c>
       <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8501,6 +9299,8 @@
       </c>
       <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8530,6 +9330,8 @@
       </c>
       <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8555,6 +9357,8 @@
       <c r="G270" t="inlineStr"/>
       <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8584,6 +9388,8 @@
       </c>
       <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8613,6 +9419,8 @@
       </c>
       <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8642,6 +9450,8 @@
       </c>
       <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8671,6 +9481,8 @@
       </c>
       <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -8700,6 +9512,8 @@
       </c>
       <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8729,6 +9543,8 @@
       </c>
       <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8758,6 +9574,8 @@
       </c>
       <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8787,6 +9605,8 @@
       </c>
       <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8816,6 +9636,8 @@
       </c>
       <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8845,6 +9667,8 @@
       </c>
       <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -8882,6 +9706,8 @@
       </c>
       <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8919,6 +9745,8 @@
       </c>
       <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8948,6 +9776,8 @@
       </c>
       <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8977,6 +9807,8 @@
       </c>
       <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9006,6 +9838,8 @@
       </c>
       <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9031,6 +9865,8 @@
       <c r="G286" t="inlineStr"/>
       <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9060,6 +9896,8 @@
       </c>
       <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9097,6 +9935,8 @@
       </c>
       <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9126,6 +9966,8 @@
       </c>
       <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -9155,6 +9997,8 @@
       </c>
       <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -9192,6 +10036,8 @@
       </c>
       <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -9221,6 +10067,8 @@
       </c>
       <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -9250,6 +10098,8 @@
       </c>
       <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -9279,6 +10129,8 @@
       </c>
       <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -9308,6 +10160,8 @@
       </c>
       <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -9337,6 +10191,8 @@
       </c>
       <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -9374,6 +10230,8 @@
       </c>
       <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -9403,6 +10261,8 @@
       </c>
       <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -9432,6 +10292,8 @@
       </c>
       <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -9461,6 +10323,8 @@
       </c>
       <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -9490,6 +10354,8 @@
       </c>
       <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr"/>
+      <c r="J301" t="inlineStr"/>
+      <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -9519,6 +10385,8 @@
       </c>
       <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr"/>
+      <c r="J302" t="inlineStr"/>
+      <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -9548,6 +10416,8 @@
       </c>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr"/>
+      <c r="J303" t="inlineStr"/>
+      <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -9577,6 +10447,8 @@
       </c>
       <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr"/>
+      <c r="J304" t="inlineStr"/>
+      <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -9606,6 +10478,8 @@
       </c>
       <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr"/>
+      <c r="J305" t="inlineStr"/>
+      <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -9635,6 +10509,8 @@
       </c>
       <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr"/>
+      <c r="J306" t="inlineStr"/>
+      <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -9672,6 +10548,8 @@
       </c>
       <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr"/>
+      <c r="J307" t="inlineStr"/>
+      <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -9701,6 +10579,8 @@
       </c>
       <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr"/>
+      <c r="J308" t="inlineStr"/>
+      <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -9726,6 +10606,8 @@
       <c r="G309" t="inlineStr"/>
       <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
+      <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -9755,6 +10637,8 @@
       </c>
       <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr"/>
+      <c r="J310" t="inlineStr"/>
+      <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -9784,6 +10668,8 @@
       </c>
       <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr"/>
+      <c r="J311" t="inlineStr"/>
+      <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -9813,6 +10699,8 @@
       </c>
       <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr"/>
+      <c r="J312" t="inlineStr"/>
+      <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -9850,6 +10738,8 @@
       </c>
       <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr"/>
+      <c r="J313" t="inlineStr"/>
+      <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -9879,6 +10769,8 @@
       </c>
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
+      <c r="J314" t="inlineStr"/>
+      <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -9908,6 +10800,8 @@
       </c>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr"/>
+      <c r="J315" t="inlineStr"/>
+      <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -9937,6 +10831,8 @@
       </c>
       <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr"/>
+      <c r="J316" t="inlineStr"/>
+      <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -9974,6 +10870,8 @@
       </c>
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -10003,6 +10901,8 @@
       </c>
       <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -10032,6 +10932,8 @@
       </c>
       <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr"/>
+      <c r="J319" t="inlineStr"/>
+      <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -10061,6 +10963,8 @@
       </c>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
+      <c r="J320" t="inlineStr"/>
+      <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -10090,6 +10994,8 @@
       </c>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
+      <c r="J321" t="inlineStr"/>
+      <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -10119,6 +11025,8 @@
       </c>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr"/>
+      <c r="J322" t="inlineStr"/>
+      <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -10148,6 +11056,8 @@
       </c>
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr"/>
+      <c r="J323" t="inlineStr"/>
+      <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -10177,6 +11087,8 @@
       </c>
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
+      <c r="J324" t="inlineStr"/>
+      <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -10206,6 +11118,8 @@
       </c>
       <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr"/>
+      <c r="J325" t="inlineStr"/>
+      <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -10243,6 +11157,8 @@
       </c>
       <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr"/>
+      <c r="J326" t="inlineStr"/>
+      <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -10268,6 +11184,8 @@
       <c r="G327" t="inlineStr"/>
       <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr"/>
+      <c r="J327" t="inlineStr"/>
+      <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -10281,7 +11199,7 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -10297,6 +11215,12 @@
       </c>
       <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr"/>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>П1</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -10306,26 +11230,32 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Биология (база)</t>
+          <t>История Беларуси (база)</t>
         </is>
       </c>
       <c r="C329" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Биология (база)·10</t>
+          <t>История Беларуси (база)·10</t>
         </is>
       </c>
       <c r="E329" t="inlineStr"/>
       <c r="F329" t="inlineStr"/>
       <c r="G329" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr"/>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>П5</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -10335,26 +11265,32 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Физика</t>
+          <t>Биология (база)</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Физика·10</t>
+          <t>Биология (база)·10</t>
         </is>
       </c>
       <c r="E330" t="inlineStr"/>
       <c r="F330" t="inlineStr"/>
       <c r="G330" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr"/>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>П1</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -10364,26 +11300,32 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>История Беларуси (проф)</t>
+          <t>Биология (база)</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>История Беларуси (проф)·10</t>
+          <t>Биология (база)·10</t>
         </is>
       </c>
       <c r="E331" t="inlineStr"/>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr"/>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>П4</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -10393,26 +11335,28 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Химия (проф)</t>
+          <t>Физика</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Химия (проф)·10</t>
+          <t>Физика·10</t>
         </is>
       </c>
       <c r="E332" t="inlineStr"/>
       <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr"/>
+      <c r="J332" t="inlineStr"/>
+      <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -10422,7 +11366,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Математика</t>
+          <t>История Беларуси (проф)</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -10430,18 +11374,24 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Математика·10</t>
+          <t>История Беларуси (проф)·10</t>
         </is>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr"/>
       <c r="G333" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr"/>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>П2</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -10451,26 +11401,32 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Белорусская литература</t>
+          <t>Химия (проф)</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Белорусская литература·10</t>
+          <t>Химия (проф)·10</t>
         </is>
       </c>
       <c r="E334" t="inlineStr"/>
       <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr"/>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>П2</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -10480,26 +11436,28 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Белорусский язык</t>
+          <t>Математика</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Белорусский язык·10</t>
+          <t>Математика·10</t>
         </is>
       </c>
       <c r="E335" t="inlineStr"/>
       <c r="F335" t="inlineStr"/>
       <c r="G335" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr"/>
+      <c r="J335" t="inlineStr"/>
+      <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -10509,7 +11467,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Обществоведение (проф)</t>
+          <t>Белорусская литература</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -10517,18 +11475,20 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Обществоведение (проф)·10</t>
+          <t>Белорусская литература·10</t>
         </is>
       </c>
       <c r="E336" t="inlineStr"/>
       <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr"/>
+      <c r="J336" t="inlineStr"/>
+      <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -10538,26 +11498,28 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Биология (проф)</t>
+          <t>Белорусский язык</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>Биология (проф)·10</t>
+          <t>Белорусский язык·10</t>
         </is>
       </c>
       <c r="E337" t="inlineStr"/>
       <c r="F337" t="inlineStr"/>
       <c r="G337" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr"/>
+      <c r="J337" t="inlineStr"/>
+      <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -10567,7 +11529,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Обществоведение (проф)</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -10575,26 +11537,24 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Английский язык·10</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Английский язык·10·2</t>
-        </is>
-      </c>
+          <t>Обществоведение (проф)·10</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr"/>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>П3</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -10604,26 +11564,32 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Обществоведение (база)</t>
+          <t>Биология (проф)</t>
         </is>
       </c>
       <c r="C339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Обществоведение (база)·10</t>
+          <t>Биология (проф)·10</t>
         </is>
       </c>
       <c r="E339" t="inlineStr"/>
       <c r="F339" t="inlineStr"/>
       <c r="G339" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr"/>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>П3</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -10633,7 +11599,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Классный час</t>
+          <t>Биология (проф)</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -10641,7 +11607,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Классный руководитель·10А</t>
+          <t>Биология (проф)·10</t>
         </is>
       </c>
       <c r="E340" t="inlineStr"/>
@@ -10653,6 +11619,12 @@
       </c>
       <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>П6</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -10662,26 +11634,28 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Химия (база)</t>
+          <t>Биология (проф)</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Химия (база)·10</t>
+          <t>Биология (проф)·10</t>
         </is>
       </c>
       <c r="E341" t="inlineStr"/>
       <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr"/>
+      <c r="J341" t="inlineStr"/>
+      <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -10691,15 +11665,15 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Информатика</t>
+          <t>Английский язык</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Информатика·10</t>
+          <t>Английский язык·10</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -10709,26 +11683,28 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Информатика·10·2</t>
+          <t>Английский язык·10·2</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr"/>
+      <c r="J342" t="inlineStr"/>
+      <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>10Б</t>
+          <t>10А</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Черчение</t>
+          <t>Обществоведение (база)</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -10736,57 +11712,65 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Черчение·10</t>
+          <t>Обществоведение (база)·10</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
       <c r="F343" t="inlineStr"/>
       <c r="G343" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr"/>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>П4</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>10Б</t>
+          <t>10А</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Русский язык</t>
+          <t>Классный час</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Русский язык·10</t>
+          <t>Классный руководитель·10А</t>
         </is>
       </c>
       <c r="E344" t="inlineStr"/>
       <c r="F344" t="inlineStr"/>
       <c r="G344" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr"/>
+      <c r="J344" t="inlineStr"/>
+      <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>10Б</t>
+          <t>10А</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ДМП</t>
+          <t>Химия (база)</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -10794,60 +11778,64 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>ДМП·10</t>
-        </is>
-      </c>
-      <c r="E345" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>ДМП·10·2</t>
-        </is>
-      </c>
+          <t>Химия (база)·10</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
       <c r="G345" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr"/>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>П5</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>10Б</t>
+          <t>10А</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Химия (база)</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Английский язык·10</t>
+          <t>Химия (база)·10</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
       <c r="F346" t="inlineStr"/>
       <c r="G346" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr"/>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>П6</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>10Б</t>
+          <t>10А</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -10880,6 +11868,8 @@
       </c>
       <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr"/>
+      <c r="J347" t="inlineStr"/>
+      <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -10889,7 +11879,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>География</t>
+          <t>Черчение</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -10897,18 +11887,20 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>География·10</t>
+          <t>Черчение·10</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
       <c r="F348" t="inlineStr"/>
       <c r="G348" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr"/>
+      <c r="J348" t="inlineStr"/>
+      <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -10918,26 +11910,28 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Математика</t>
+          <t>Русский язык</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Математика·10</t>
+          <t>Русский язык·10</t>
         </is>
       </c>
       <c r="E349" t="inlineStr"/>
       <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>313</t>
         </is>
       </c>
       <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -10947,26 +11941,36 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>История РБ в контексте мировой истории</t>
+          <t>ДМП</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>История РБ в контексте мировой истории·10</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
+          <t>ДМП·10</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>ДМП·10·2</t>
+        </is>
+      </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -10976,26 +11980,28 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Белорусский язык</t>
+          <t>Английский язык</t>
         </is>
       </c>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Белорусский язык·10</t>
+          <t>Английский язык·10</t>
         </is>
       </c>
       <c r="E351" t="inlineStr"/>
       <c r="F351" t="inlineStr"/>
       <c r="G351" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>207</t>
         </is>
       </c>
       <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr"/>
+      <c r="J351" t="inlineStr"/>
+      <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -11005,26 +12011,36 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Физика</t>
+          <t>Информатика</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Физика·10</t>
-        </is>
-      </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
+          <t>Информатика·10</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Информатика·10·2</t>
+        </is>
+      </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -11034,22 +12050,28 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Физическая культура и здоровье</t>
+          <t>География</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Физическая культура и здоровье·10</t>
+          <t>География·10</t>
         </is>
       </c>
       <c r="E353" t="inlineStr"/>
       <c r="F353" t="inlineStr"/>
-      <c r="G353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -11059,26 +12081,28 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Химия</t>
+          <t>Математика</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Химия·10</t>
+          <t>Математика·10</t>
         </is>
       </c>
       <c r="E354" t="inlineStr"/>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>311</t>
         </is>
       </c>
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -11088,7 +12112,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Белорусская литература</t>
+          <t>История РБ в контексте мировой истории</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -11096,18 +12120,20 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Белорусская литература·10</t>
+          <t>История РБ в контексте мировой истории·10</t>
         </is>
       </c>
       <c r="E355" t="inlineStr"/>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -11117,7 +12143,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Классный час</t>
+          <t>Белорусский язык</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -11125,18 +12151,20 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Классный руководитель·10Б</t>
+          <t>Белорусский язык·10</t>
         </is>
       </c>
       <c r="E356" t="inlineStr"/>
       <c r="F356" t="inlineStr"/>
       <c r="G356" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -11146,26 +12174,28 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Биология</t>
+          <t>Физика</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Биология·10</t>
+          <t>Физика·10</t>
         </is>
       </c>
       <c r="E357" t="inlineStr"/>
       <c r="F357" t="inlineStr"/>
       <c r="G357" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr"/>
+      <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -11175,26 +12205,24 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Обществоведение</t>
+          <t>Физическая культура и здоровье</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Обществоведение·10</t>
+          <t>Физическая культура и здоровье·10</t>
         </is>
       </c>
       <c r="E358" t="inlineStr"/>
       <c r="F358" t="inlineStr"/>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
+      <c r="G358" t="inlineStr"/>
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -11204,65 +12232,69 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Русская литература</t>
+          <t>Химия</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Русская литература·10</t>
+          <t>Химия·10</t>
         </is>
       </c>
       <c r="E359" t="inlineStr"/>
       <c r="F359" t="inlineStr"/>
       <c r="G359" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr"/>
+      <c r="J359" t="inlineStr"/>
+      <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>11А</t>
+          <t>10Б</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Математика</t>
+          <t>Белорусская литература</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Математика·11</t>
+          <t>Белорусская литература·10</t>
         </is>
       </c>
       <c r="E360" t="inlineStr"/>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr"/>
+      <c r="J360" t="inlineStr"/>
+      <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>11А</t>
+          <t>10Б</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>ДМП</t>
+          <t>Классный час</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -11270,36 +12302,30 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>ДМП·11</t>
-        </is>
-      </c>
-      <c r="E361" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>ДМП·11·2</t>
-        </is>
-      </c>
+          <t>Классный руководитель·10Б</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>316</t>
         </is>
       </c>
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr"/>
+      <c r="J361" t="inlineStr"/>
+      <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>11А</t>
+          <t>10Б</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Белорусский язык</t>
+          <t>Биология</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -11307,53 +12333,61 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Белорусский язык·11</t>
+          <t>Биология·10</t>
         </is>
       </c>
       <c r="E362" t="inlineStr"/>
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>314</t>
         </is>
       </c>
       <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr"/>
+      <c r="J362" t="inlineStr"/>
+      <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>11А</t>
+          <t>10Б</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Физическая культура и здоровье</t>
+          <t>Обществоведение</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Физическая культура и здоровье·11</t>
+          <t>Обществоведение·10</t>
         </is>
       </c>
       <c r="E363" t="inlineStr"/>
       <c r="F363" t="inlineStr"/>
-      <c r="G363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
       <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr"/>
+      <c r="J363" t="inlineStr"/>
+      <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>11А</t>
+          <t>10Б</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Белорусская литература</t>
+          <t>Русская литература</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -11361,18 +12395,20 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Белорусская литература·11</t>
+          <t>Русская литература·10</t>
         </is>
       </c>
       <c r="E364" t="inlineStr"/>
       <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>302</t>
         </is>
       </c>
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
+      <c r="J364" t="inlineStr"/>
+      <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -11382,26 +12418,28 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Русская литература</t>
+          <t>Математика</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Русская литература·11</t>
+          <t>Математика·11</t>
         </is>
       </c>
       <c r="E365" t="inlineStr"/>
       <c r="F365" t="inlineStr"/>
       <c r="G365" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr"/>
+      <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -11411,26 +12449,36 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Химия (проф)</t>
+          <t>ДМП</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Химия (проф)·11</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
+          <t>ДМП·11</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>ДМП·11·2</t>
+        </is>
+      </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr"/>
+      <c r="J366" t="inlineStr"/>
+      <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -11440,7 +12488,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Биология (база)</t>
+          <t>Белорусский язык</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -11448,18 +12496,20 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Биология (база)·11</t>
+          <t>Белорусский язык·11</t>
         </is>
       </c>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
       <c r="G367" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr"/>
+      <c r="J367" t="inlineStr"/>
+      <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -11469,26 +12519,24 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Физика</t>
+          <t>Физическая культура и здоровье</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Физика·11</t>
+          <t>Физическая культура и здоровье·11</t>
         </is>
       </c>
       <c r="E368" t="inlineStr"/>
       <c r="F368" t="inlineStr"/>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
+      <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr"/>
+      <c r="J368" t="inlineStr"/>
+      <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -11498,7 +12546,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Астрономия</t>
+          <t>Белорусская литература</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -11506,18 +12554,20 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Астрономия·11</t>
+          <t>Белорусская литература·11</t>
         </is>
       </c>
       <c r="E369" t="inlineStr"/>
       <c r="F369" t="inlineStr"/>
       <c r="G369" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr"/>
+      <c r="J369" t="inlineStr"/>
+      <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -11527,26 +12577,28 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Английский язык (проф)</t>
+          <t>Русская литература</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Английский язык (проф)·11</t>
+          <t>Русская литература·11</t>
         </is>
       </c>
       <c r="E370" t="inlineStr"/>
       <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr"/>
+      <c r="J370" t="inlineStr"/>
+      <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -11556,26 +12608,32 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Английский язык (база)</t>
+          <t>Химия (проф)</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Английский язык (база)·11</t>
+          <t>Химия (проф)·11</t>
         </is>
       </c>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr"/>
       <c r="G371" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr"/>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>П1</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -11585,7 +12643,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>История РБ в контексте мировой истории</t>
+          <t>Химия (проф)</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -11593,18 +12651,24 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>История РБ в контексте мировой истории·11</t>
+          <t>Химия (проф)·11</t>
         </is>
       </c>
       <c r="E372" t="inlineStr"/>
       <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr"/>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>П2</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -11614,26 +12678,32 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Биология (проф)</t>
+          <t>Химия (проф)</t>
         </is>
       </c>
       <c r="C373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Биология (проф)·11</t>
+          <t>Химия (проф)·11</t>
         </is>
       </c>
       <c r="E373" t="inlineStr"/>
       <c r="F373" t="inlineStr"/>
       <c r="G373" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr"/>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>П3</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -11643,26 +12713,32 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Обществоведение (проф)</t>
+          <t>Биология (база)</t>
         </is>
       </c>
       <c r="C374" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Обществоведение (проф)·11</t>
+          <t>Биология (база)·11</t>
         </is>
       </c>
       <c r="E374" t="inlineStr"/>
       <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr"/>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>П1</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -11672,7 +12748,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Классный час</t>
+          <t>Биология (база)</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -11680,18 +12756,24 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Классный руководитель·11А</t>
+          <t>Биология (база)·11</t>
         </is>
       </c>
       <c r="E375" t="inlineStr"/>
       <c r="F375" t="inlineStr"/>
       <c r="G375" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>П3</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -11701,26 +12783,28 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Русский язык</t>
+          <t>Физика</t>
         </is>
       </c>
       <c r="C376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Русский язык·11</t>
+          <t>Физика·11</t>
         </is>
       </c>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
       <c r="G376" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr"/>
+      <c r="J376" t="inlineStr"/>
+      <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -11730,7 +12814,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>География</t>
+          <t>Астрономия</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -11738,18 +12822,20 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>География·11</t>
+          <t>Астрономия·11</t>
         </is>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
       <c r="G377" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr"/>
+      <c r="J377" t="inlineStr"/>
+      <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -11759,7 +12845,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Информатика</t>
+          <t>Английский язык (проф)</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -11767,26 +12853,24 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Информатика·11</t>
-        </is>
-      </c>
-      <c r="E378" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>Информатика·11·2</t>
-        </is>
-      </c>
+          <t>Английский язык (проф)·11</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr"/>
       <c r="G378" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr"/>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>П4</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -11796,7 +12880,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Химия (база)</t>
+          <t>Английский язык (проф)</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -11804,18 +12888,24 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Химия (база)·11</t>
+          <t>Английский язык (проф)·11</t>
         </is>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
       <c r="G379" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>П5</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -11825,65 +12915,77 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Обществоведение (база)</t>
+          <t>Английский язык (проф)</t>
         </is>
       </c>
       <c r="C380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Обществоведение (база)·11</t>
+          <t>Английский язык (проф)·11</t>
         </is>
       </c>
       <c r="E380" t="inlineStr"/>
       <c r="F380" t="inlineStr"/>
       <c r="G380" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>П6</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Белорусский язык</t>
+          <t>Английский язык (база)</t>
         </is>
       </c>
       <c r="C381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Белорусский язык·11</t>
+          <t>Английский язык (база)·11</t>
         </is>
       </c>
       <c r="E381" t="inlineStr"/>
       <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>П4</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>ДМП</t>
+          <t>Английский язык (база)</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -11891,90 +12993,100 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>ДМП·11</t>
-        </is>
-      </c>
-      <c r="E382" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>ДМП·11·2</t>
-        </is>
-      </c>
+          <t>Английский язык (база)·11</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr"/>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>П5</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Белорусская литература</t>
+          <t>История РБ в контексте мировой истории</t>
         </is>
       </c>
       <c r="C383" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Белорусская литература·11</t>
+          <t>История РБ в контексте мировой истории·11</t>
         </is>
       </c>
       <c r="E383" t="inlineStr"/>
       <c r="F383" t="inlineStr"/>
       <c r="G383" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr"/>
+      <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Физическая культура и здоровье</t>
+          <t>Биология (проф)</t>
         </is>
       </c>
       <c r="C384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Физическая культура и здоровье·11</t>
+          <t>Биология (проф)·11</t>
         </is>
       </c>
       <c r="E384" t="inlineStr"/>
       <c r="F384" t="inlineStr"/>
-      <c r="G384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
       <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>П6</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Русская литература</t>
+          <t>Биология (проф)</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -11982,57 +13094,65 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Русская литература·11</t>
+          <t>Биология (проф)·11</t>
         </is>
       </c>
       <c r="E385" t="inlineStr"/>
       <c r="F385" t="inlineStr"/>
       <c r="G385" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>География</t>
+          <t>Обществоведение (проф)</t>
         </is>
       </c>
       <c r="C386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>География·11</t>
+          <t>Обществоведение (проф)·11</t>
         </is>
       </c>
       <c r="E386" t="inlineStr"/>
       <c r="F386" t="inlineStr"/>
       <c r="G386" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>П2</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Информатика</t>
+          <t>Классный час</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -12040,160 +13160,166 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Информатика·11</t>
-        </is>
-      </c>
-      <c r="E387" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>Информатика·11·2</t>
-        </is>
-      </c>
+          <t>Классный руководитель·11А</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr"/>
       <c r="G387" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>История РБ в контексте мировой истории</t>
+          <t>Русский язык</t>
         </is>
       </c>
       <c r="C388" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>История РБ в контексте мировой истории·11</t>
+          <t>Русский язык·11</t>
         </is>
       </c>
       <c r="E388" t="inlineStr"/>
       <c r="F388" t="inlineStr"/>
       <c r="G388" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Химия</t>
+          <t>География</t>
         </is>
       </c>
       <c r="C389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Химия·11</t>
+          <t>География·11</t>
         </is>
       </c>
       <c r="E389" t="inlineStr"/>
       <c r="F389" t="inlineStr"/>
       <c r="G389" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Математика</t>
+          <t>Информатика</t>
         </is>
       </c>
       <c r="C390" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Математика·11</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
+          <t>Информатика·11</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Информатика·11·2</t>
+        </is>
+      </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>309</t>
         </is>
       </c>
       <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Английский язык</t>
+          <t>Химия (база)</t>
         </is>
       </c>
       <c r="C391" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Английский язык·11</t>
-        </is>
-      </c>
-      <c r="E391" t="inlineStr">
-        <is>
-          <t>A/B</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>Английский язык·11·2</t>
-        </is>
-      </c>
+          <t>Химия (база)·11</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr"/>
       <c r="G391" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr"/>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>П7</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>11Б</t>
+          <t>11А</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Астрономия</t>
+          <t>Обществоведение (база)</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -12201,18 +13327,24 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Астрономия·11</t>
+          <t>Обществоведение (база)·11</t>
         </is>
       </c>
       <c r="E392" t="inlineStr"/>
       <c r="F392" t="inlineStr"/>
       <c r="G392" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>П7</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -12222,26 +13354,28 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Физика</t>
+          <t>Белорусский язык</t>
         </is>
       </c>
       <c r="C393" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Физика·11</t>
+          <t>Белорусский язык·11</t>
         </is>
       </c>
       <c r="E393" t="inlineStr"/>
       <c r="F393" t="inlineStr"/>
       <c r="G393" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -12251,26 +13385,36 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Биология</t>
+          <t>ДМП</t>
         </is>
       </c>
       <c r="C394" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Биология·11</t>
-        </is>
-      </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
+          <t>ДМП·11</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>ДМП·11·2</t>
+        </is>
+      </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr"/>
+      <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -12280,7 +13424,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Классный час</t>
+          <t>Белорусская литература</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -12288,18 +13432,20 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Классный руководитель·11Б</t>
+          <t>Белорусская литература·11</t>
         </is>
       </c>
       <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -12309,26 +13455,24 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Русский язык</t>
+          <t>Физическая культура и здоровье</t>
         </is>
       </c>
       <c r="C396" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Русский язык·11</t>
+          <t>Физическая культура и здоровье·11</t>
         </is>
       </c>
       <c r="E396" t="inlineStr"/>
       <c r="F396" t="inlineStr"/>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
+      <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -12338,26 +13482,416 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Обществоведение</t>
+          <t>Русская литература</t>
         </is>
       </c>
       <c r="C397" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Обществоведение·11</t>
+          <t>Русская литература·11</t>
         </is>
       </c>
       <c r="E397" t="inlineStr"/>
       <c r="F397" t="inlineStr"/>
       <c r="G397" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>География</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>1</v>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>География·11</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr"/>
+      <c r="K398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Информатика</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>1</v>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Информатика·11</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Информатика·11·2</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr"/>
+      <c r="K399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>История РБ в контексте мировой истории</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>2</v>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>История РБ в контексте мировой истории·11</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="inlineStr"/>
+      <c r="K400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Химия</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>2</v>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Химия·11</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="inlineStr"/>
+      <c r="K401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Математика</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>6</v>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Математика·11</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="inlineStr"/>
+      <c r="K402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Английский язык</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>2</v>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Английский язык·11</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Английский язык·11·2</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Астрономия</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Астрономия·11</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Физика</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>4</v>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Физика·11</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Биология</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>2</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Биология·11</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Классный час</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>1</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Классный руководитель·11Б</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Русский язык</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>1</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Русский язык·11</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>11Б</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Обществоведение</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>1</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Обществоведение·11</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
